--- a/ig/nr-resolve-example-error/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/nr-resolve-example-error/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T17:10:19+00:00</t>
+    <t>2024-02-02T09:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-resolve-example-error/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/nr-resolve-example-error/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-02T09:57:39+00:00</t>
+    <t>2024-02-02T10:00:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
